--- a/outputs/ber_results_by_type_and_band.xlsx
+++ b/outputs/ber_results_by_type_and_band.xlsx
@@ -11693,7 +11693,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DEAP-calculated delivered energy for space heating, water heating, lighting and pumps/fans under standard occupancy, before deducting on-site PV; appliances and cooking are not included. Electric heating end uses are rebuilt as primary energy / the electricity factor in force (the file stores primary / 2.08)</t>
+          <t>DEAP-calculated delivered energy for space heating, water heating, lighting and pumps/fans under standard occupancy, before deducting on-site PV; appliances and cooking are not included. Electric heating end uses are rebuilt as primary energy / the electricity factor in force (the file stores most electric heating as primary / 2.08)</t>
         </is>
       </c>
     </row>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Renewable Energy Ratio, filled from Nov 2019 only</t>
+          <t>Renewable Energy Ratio. Filled for all certificates assessed from 2021 and most assessed from Dec 2019, but missing for most assessed in Nov 2019 and Aug-Nov 2020; statistics use certificates that have it (base = rer_n)</t>
         </is>
       </c>
     </row>
